--- a/data/Hermenches/cost/total_demand.xlsx
+++ b/data/Hermenches/cost/total_demand.xlsx
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>104308.2596830278</v>
+        <v>104373.9745201315</v>
       </c>
     </row>
   </sheetData>
